--- a/outputs/tables/sample_composition.xlsx
+++ b/outputs/tables/sample_composition.xlsx
@@ -500,31 +500,31 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>573</v>
+        <v>497</v>
       </c>
       <c r="D2" t="n">
         <v>25</v>
       </c>
       <c r="E2" t="n">
-        <v>4646</v>
+        <v>4405</v>
       </c>
       <c r="F2" t="n">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="G2" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="H2" t="n">
-        <v>773</v>
+        <v>721</v>
       </c>
       <c r="I2" t="n">
-        <v>16.6</v>
+        <v>16.4</v>
       </c>
       <c r="J2" t="n">
         <v>62</v>
       </c>
       <c r="K2" t="n">
-        <v>18.7</v>
+        <v>19</v>
       </c>
       <c r="L2" t="n">
         <v>16</v>
@@ -545,31 +545,31 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>573</v>
+        <v>497</v>
       </c>
       <c r="D3" t="n">
         <v>25</v>
       </c>
       <c r="E3" t="n">
-        <v>4646</v>
+        <v>4405</v>
       </c>
       <c r="F3" t="n">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="G3" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="H3" t="n">
-        <v>773</v>
+        <v>721</v>
       </c>
       <c r="I3" t="n">
-        <v>16.6</v>
+        <v>16.4</v>
       </c>
       <c r="J3" t="n">
         <v>62</v>
       </c>
       <c r="K3" t="n">
-        <v>18.7</v>
+        <v>19</v>
       </c>
       <c r="L3" t="n">
         <v>16</v>
@@ -595,31 +595,31 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>534</v>
+        <v>474</v>
       </c>
       <c r="D4" t="n">
         <v>25</v>
       </c>
       <c r="E4" t="n">
-        <v>4073</v>
+        <v>3873</v>
       </c>
       <c r="F4" t="n">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="G4" t="n">
-        <v>13.3</v>
+        <v>12.8</v>
       </c>
       <c r="H4" t="n">
-        <v>727</v>
+        <v>685</v>
       </c>
       <c r="I4" t="n">
-        <v>17.8</v>
+        <v>17.7</v>
       </c>
       <c r="J4" t="n">
         <v>62</v>
       </c>
       <c r="K4" t="n">
-        <v>20.3</v>
+        <v>20.5</v>
       </c>
       <c r="L4" t="n">
         <v>16</v>
@@ -640,31 +640,31 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>534</v>
+        <v>474</v>
       </c>
       <c r="D5" t="n">
         <v>25</v>
       </c>
       <c r="E5" t="n">
-        <v>4073</v>
+        <v>3873</v>
       </c>
       <c r="F5" t="n">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="G5" t="n">
-        <v>13.3</v>
+        <v>12.8</v>
       </c>
       <c r="H5" t="n">
-        <v>727</v>
+        <v>685</v>
       </c>
       <c r="I5" t="n">
-        <v>17.8</v>
+        <v>17.7</v>
       </c>
       <c r="J5" t="n">
         <v>62</v>
       </c>
       <c r="K5" t="n">
-        <v>20.3</v>
+        <v>20.5</v>
       </c>
       <c r="L5" t="n">
         <v>16</v>
@@ -685,31 +685,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>486</v>
+        <v>442</v>
       </c>
       <c r="D6" t="n">
         <v>25</v>
       </c>
       <c r="E6" t="n">
-        <v>3539</v>
+        <v>3396</v>
       </c>
       <c r="F6" t="n">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="G6" t="n">
-        <v>12.6</v>
+        <v>12.3</v>
       </c>
       <c r="H6" t="n">
-        <v>687</v>
+        <v>654</v>
       </c>
       <c r="I6" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="J6" t="n">
         <v>62</v>
       </c>
       <c r="K6" t="n">
-        <v>22.1</v>
+        <v>22.4</v>
       </c>
       <c r="L6" t="n">
         <v>16</v>
@@ -730,31 +730,31 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>486</v>
+        <v>442</v>
       </c>
       <c r="D7" t="n">
         <v>25</v>
       </c>
       <c r="E7" t="n">
-        <v>3539</v>
+        <v>3396</v>
       </c>
       <c r="F7" t="n">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="G7" t="n">
-        <v>12.6</v>
+        <v>12.3</v>
       </c>
       <c r="H7" t="n">
-        <v>687</v>
+        <v>654</v>
       </c>
       <c r="I7" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="J7" t="n">
         <v>62</v>
       </c>
       <c r="K7" t="n">
-        <v>22.1</v>
+        <v>22.4</v>
       </c>
       <c r="L7" t="n">
         <v>16</v>
